--- a/XYZ.xlsx
+++ b/XYZ.xlsx
@@ -48,7 +48,7 @@
     <x:t>Short Description</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-14 02:22</x:t>
+    <x:t>2026-04-14</x:t>
   </x:si>
   <x:si>
     <x:t>Atanu</x:t>
@@ -66,9 +66,6 @@
     <x:t>Just Testing</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-14 03:29</x:t>
-  </x:si>
-  <x:si>
     <x:t>Yash</x:t>
   </x:si>
   <x:si>
@@ -79,9 +76,6 @@
   </x:si>
   <x:si>
     <x:t>Okk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-14</x:t>
   </x:si>
   <x:si>
     <x:t>Final Testing</x:t>
@@ -802,8 +796,8 @@
     <x:cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </x:cellStyles>
   <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{DB8C3F9A-A1F6-436F-9C39-29967072558B}"/>
-    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{8628F7F4-1034-413C-A022-2D7B8581FDE8}"/>
+    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{3258B4C4-250D-46B9-A0BF-C1FF7C480DB0}"/>
+    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{EA2E581F-EF35-458F-8A63-931874B10B14}"/>
   </x:tableStyles>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1073,7 +1067,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F2"/>
+  <x:dimension ref="A1:F5"/>
   <x:sheetFormatPr defaultColWidth="10.282054" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10.285714" style="0" customWidth="1"/>
@@ -1125,42 +1119,42 @@
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="C3" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="D3" s="2" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
